--- a/artfynd/A 31503-2025 artfynd.xlsx
+++ b/artfynd/A 31503-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105165211</v>
+        <v>105165214</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608770.0293026986</v>
+        <v>608723</v>
       </c>
       <c r="R2" t="n">
-        <v>7038737.544539756</v>
+        <v>7038718</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105165210</v>
+        <v>105165211</v>
       </c>
       <c r="B3" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608780.1213210418</v>
+        <v>608770</v>
       </c>
       <c r="R3" t="n">
-        <v>7038730.727573752</v>
+        <v>7038738</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105165212</v>
+        <v>105165210</v>
       </c>
       <c r="B4" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608773.9209442635</v>
+        <v>608780</v>
       </c>
       <c r="R4" t="n">
-        <v>7038741.705259522</v>
+        <v>7038731</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,6 +971,107 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>105165212</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608774</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7038742</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>

--- a/artfynd/A 31503-2025 artfynd.xlsx
+++ b/artfynd/A 31503-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165214</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165211</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165210</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165212</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>